--- a/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -484,14 +484,6 @@
 　- 1020 ヒンドゥー教  
 　- 1023 イスラム教  
 など</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace</t>
@@ -538,6 +530,14 @@
 　- 2111-3 フランス人  
 　- 2112-1 ドイツ人  
 など</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -3405,10 +3405,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3428,13 +3428,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>136</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>82</v>
@@ -3456,16 +3456,16 @@
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3524,10 +3524,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3547,13 +3547,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>136</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
@@ -3575,16 +3575,16 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3643,10 +3643,10 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
@@ -5057,7 +5057,7 @@
         <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>259</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
@@ -828,7 +828,7 @@
 </t>
   </si>
   <si>
-    <t>人の名前情報、その一部分と使い方</t>
+    <t>A name associated with the patient</t>
   </si>
   <si>
     <t>個人に関連付けられた名前。</t>
@@ -846,14 +846,13 @@
     <t>複数の名前で患者を追跡できる必要がある。例としては、正式名とパートナー名がある。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
-  </si>
-  <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>XPN</t>
+    <t>name</t>
+  </si>
+  <si>
+    <t>.patient.name</t>
+  </si>
+  <si>
+    <t>PID-5, PID-9</t>
   </si>
   <si>
     <t>Patient.telecom</t>
@@ -1620,9 +1619,6 @@
     <t>連絡先は名前で識別する必要があるが、その連絡先に複数の名前が必要になることはまれである。</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>NK1-2</t>
   </si>
   <si>
@@ -1721,6 +1717,10 @@
   </si>
   <si>
     <t>患者が現地の言語を話さない場合、通訳が必要になる場合があるため、話せる言語と習熟度は、患者と関心のある他の人の両方にとって注意すべき重要な事項である。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>LanguageCommunication</t>
@@ -4984,7 +4984,7 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>254</v>
@@ -5057,16 +5057,16 @@
         <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AK24" t="s" s="2">
+      <c r="AL24" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>82</v>
@@ -8946,7 +8946,7 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>489</v>
+        <v>259</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>185</v>
@@ -8955,7 +8955,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8963,10 +8963,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8992,16 +8992,16 @@
         <v>263</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9050,7 +9050,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9074,7 +9074,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9111,14 +9111,14 @@
         <v>339</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9167,7 +9167,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9191,7 +9191,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9199,10 +9199,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9231,11 +9231,11 @@
         <v>312</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9284,7 +9284,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9308,7 +9308,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9316,10 +9316,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9345,16 +9345,16 @@
         <v>237</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9403,7 +9403,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9412,13 +9412,13 @@
         <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>185</v>
@@ -9427,7 +9427,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9435,10 +9435,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9464,10 +9464,10 @@
         <v>229</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9518,7 +9518,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9533,7 +9533,7 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>185</v>
@@ -9550,10 +9550,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9579,16 +9579,16 @@
         <v>461</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9637,7 +9637,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9649,7 +9649,7 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>259</v>
+        <v>522</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>523</v>
@@ -10477,7 +10477,7 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>556</v>
@@ -10593,7 +10593,7 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>259</v>
+        <v>522</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>562</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -272,7 +272,7 @@
     <t>医療サービスを受けている個人または動物に関する情報</t>
   </si>
   <si>
-    <t>ケアまたはその他の健康関連サービスを受けている個人または動物に関する人口統計およびその他の管理情報。</t>
+    <t>ケアまたはその他の健康関連サービスを受けている個人または動物に関する基本情報およびその他の管理情報。</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -374,7 +374,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -469,7 +469,7 @@
     <t>religion</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-religion}
+    <t xml:space="preserve">Extension {patient-religion|4.0.1}
 </t>
   </si>
   <si>
@@ -492,7 +492,7 @@
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace}
+    <t xml:space="preserve">Extension {patient-birthPlace|4.0.1}
 </t>
   </si>
   <si>
@@ -677,7 +677,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.3.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -695,7 +695,9 @@
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>Patient.identifier.system には、urn:oid:1.2.392.100495.20.3.51.医療機関識別OID番号を使用する。 医療機関識別OID番号は患者IDの発行者である機関の医療機関コード（１０桁）の先頭に１をつけた11桁とする。医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。  ```例：医療機関コード「1312345670」の場合「urn:oid:1.2.392.100495.20.3.51.11312345670」```　なお、urn:oid:1.2.392.100495.20.3.51の部分は、「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」表19 識別子名前空間一覧において医療機関等の患者IDとして割り当てられたOIDのURL型である。地域医療連携ネットワークの地域患者IDを指定する場合も同様に、地域患者IDを識別する名前空間（IHE ITI PIX等で使用されるOID等）をsystemに使用することができる。</t>
+    <t>Patient.identifier.system には、urn:oid:1.2.392.100495.20.3.51.医療機関識別OID番号を使用する。 医療機関識別OID番号は患者IDの発行者である機関の医療機関コード（１０桁）の先頭に１をつけた11桁とする。医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。  ```例：医療機関コード「1312345670」の場合「urn:oid:1.2.392.100495.20.3.51.11312345670」```　なお、urn:oid:1.2.392.100495.20.3.51の部分は、「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」表19 識別子名前空間一覧において医療機関等の患者IDとして割り当てられたOIDのURL型である。地域医療連携ネットワークの地域患者IDを指定する場合も同様に、地域患者IDを識別する名前空間（IHE ITI PIX等で使用されるOID等）をsystemに使用することができる。
+Patient.identifier.systemには、厚生労働省が推進する全国医療情報プラットフォームや電子カルテ情報共有サービスで公開されている識別子体系、あるいは JP Core において任意の医療機関がカルテ番号として使用する値などを指定することができる。
+これ以外（例：DL：運転免許証番号、PPN：パスポート番号、BRN：血統登録番号など）については、JP Core では system の値を定義していない。</t>
   </si>
   <si>
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
@@ -1380,13 +1382,13 @@
     <t>Patient.address.country</t>
   </si>
   <si>
-    <t>国名またはISO 3166コード　(ISO 3166 2 or 3文字こーど)</t>
+    <t>国名またはISO 3166コード　(ISO 3166 2 or 3文字コード)</t>
   </si>
   <si>
     <t>国-一般的に理解されている、または一般的に受け入れられている国の国名かコード。</t>
   </si>
   <si>
-    <t>ISO 3166 3文字コードは、人間が読める国名の代わりに使用する。  ISO 3166の2文字または3文字のコード.  日本であれば、jpまたはjpn</t>
+    <t>ISO 3166 3文字コードは、人間が読める国名の代わりに使用する。  ISO 3166の2文字または3文字のコード.  日本であれば、JPまたはJPN</t>
   </si>
   <si>
     <t>Address.country</t>
@@ -1451,7 +1453,7 @@
     <t>The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.3.0</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -1594,7 +1596,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.3.0</t>
   </si>
   <si>
     <t>code</t>
@@ -2212,17 +2214,17 @@
   <dimension ref="A1:AO76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.47265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.47265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="176.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="151.41015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2231,27 +2233,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="39.97265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="80.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.921875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.26953125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="69.35546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="156.828125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="40.8125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="40.0703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="134.453125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="34.98828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="34.35546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
@@ -469,7 +469,7 @@
     <t>religion</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-religion|4.0.1}
+    <t xml:space="preserve">Extension {patient-religion|4.3.0}
 </t>
   </si>
   <si>
@@ -486,13 +486,21 @@
 など</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Patient.extension:birthPlace</t>
   </si>
   <si>
     <t>birthPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {patient-birthPlace|4.0.1}
+    <t xml:space="preserve">Extension {patient-birthPlace|4.3.0}
 </t>
   </si>
   <si>
@@ -530,14 +538,6 @@
 　- 2111-3 フランス人  
 　- 2112-1 ドイツ人  
 など</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Patient.modifierExtension</t>
@@ -3407,10 +3407,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3430,13 +3430,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>136</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>82</v>
@@ -3458,16 +3458,16 @@
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3526,10 +3526,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3549,13 +3549,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>136</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
@@ -3577,16 +3577,16 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3645,10 +3645,10 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2875" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2875" uniqueCount="586">
   <si>
     <t>Property</t>
   </si>
@@ -275,8 +275,8 @@
     <t>ケアまたはその他の健康関連サービスを受けている個人または動物に関する基本情報およびその他の管理情報。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Patient[classCode=PAT]</t>
@@ -301,13 +301,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -340,13 +340,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -359,19 +359,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -391,13 +391,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -417,19 +417,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -459,8 +459,8 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Patient.extension:religion</t>
@@ -490,8 +490,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace</t>
@@ -547,17 +547,18 @@
 user content</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -601,10 +602,10 @@
     <t>Patient.identifier.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -616,10 +617,10 @@
     <t>Patient.identifier.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -634,13 +635,13 @@
     <t>usual | official | temp | secondary | old (If known) 【詳細参照】</t>
   </si>
   <si>
-    <t>The purpose of this identifier.</t>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
   </si>
   <si>
     <t>IDの種別をValueSet(IdentifierUse)より選択する。  - usual : 一般- official : 公式（マイナンバーなど、最も信頼できると見なされる場合に使用）- temp : 一時的　- secondary : 二次利用　- old : 過去の識別子</t>
   </si>
   <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
@@ -665,13 +666,13 @@
     <t>識別子の種別 【詳細参照】</t>
   </si>
   <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>IDの種別をValueSet(Identifier Type Codes)より選択する。　- DL : 運転免許証番号　- PPN : パスポート番号　- BRN : 血統登録番号　- MR : カルテ番号、など</t>
   </si>
   <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -692,7 +693,7 @@
     <t>The namespace for the identifier value 【詳細参照】</t>
   </si>
   <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>Patient.identifier.system には、urn:oid:1.2.392.100495.20.3.51.医療機関識別OID番号を使用する。 医療機関識別OID番号は患者IDの発行者である機関の医療機関コード（１０桁）の先頭に１をつけた11桁とする。医療機関コード（１０桁）の詳細はOrganizationプロファイルの医療機関コード１０桁の説明を参照すること。  ```例：医療機関コード「1312345670」の場合「urn:oid:1.2.392.100495.20.3.51.11312345670」```　なお、urn:oid:1.2.392.100495.20.3.51の部分は、「[処方情報 HL7FHIR 記述仕様](https://std.jpfhir.jp/stddoc/ePrescriptionDataFHIR_v1x.pdf)」表19 識別子名前空間一覧において医療機関等の患者IDとして割り当てられたOIDのURL型である。地域医療連携ネットワークの地域患者IDを指定する場合も同様に、地域患者IDを識別する名前空間（IHE ITI PIX等で使用されるOID等）をsystemに使用することができる。
@@ -700,7 +701,7 @@
 これ以外（例：DL：運転免許証番号、PPN：パスポート番号、BRN：血統登録番号など）については、JP Core では system の値を定義していない。</t>
   </si>
   <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -725,7 +726,7 @@
     <t>識別子のvalueは一意である必要がある。 【詳細参照】</t>
   </si>
   <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
     <t>患者を一意的に識別するID(例えば、患者IDやカルテ番号など)を設定。</t>
@@ -750,10 +751,10 @@
 </t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>IDが使われていた/使われている期間。</t>
@@ -775,10 +776,10 @@
 </t>
   </si>
   <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
+    <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
   </si>
   <si>
     <t>IDを発行した組織（テキストのみでも可）</t>
@@ -800,7 +801,7 @@
 </t>
   </si>
   <si>
-    <t>Whether this patient's record is in active use</t>
+    <t>この患者の記録が積極的に使用されているかどうか / Whether this patient's record is in active use</t>
   </si>
   <si>
     <t>この患者記録がアクティブに使用されているかどうか。多くのシステムは、このプロパティを使用して、組織のビジネスルールに基づいて一定期間見られなかった患者など、非現在の患者としてマークする。  
@@ -814,7 +815,7 @@
     <t>患者レコードが誤って作成された場合のため、使用されないレコードとしてマークできる必要がある。</t>
   </si>
   <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+    <t>このリソースは、アクティブな要素の値が提供されていない場合、一般にアクティブであると想定されています / This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
     <t>statusCode</t>
@@ -830,7 +831,7 @@
 </t>
   </si>
   <si>
-    <t>A name associated with the patient</t>
+    <t>患者に関連付けられた名前 / A name associated with the patient</t>
   </si>
   <si>
     <t>個人に関連付けられた名前。</t>
@@ -888,16 +889,35 @@
     <t>Patient.telecom.id</t>
   </si>
   <si>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>Patient.telecom.extension</t>
   </si>
   <si>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Patient.telecom.system</t>
   </si>
   <si>
     <t>phone | fax | email | pager | url | sms | other 【詳細参照】</t>
   </si>
   <si>
-    <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
+    <t>連絡先用通信フォーム - どの通信システムを使用するには接点が必要ですか。 / Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointSystem)より選択する。  　- phone : 電話　- fax : Fax 　- email : 電子メール　- pager : ポケットベル　- url : 電話、ファックス、ポケットベル、または電子メールアドレスではなく、URLとして表される連絡先。これはWebサイト、ブログ、Skype、Twitter、Facebookなどのさまざまな機関または個人の連絡先を対象としている。電子メールアドレスには使用しないこと。　- sms : SMSメッセージの送信に使用できる連絡先（携帯電話、一部の固定電話など）  　- other : 電話、Fax、ポケットベル、または電子メールアドレスではなく、URLとして表現できない連絡先。例：内部メールアドレス。これは、URLとして表現できる連絡先（Skype、Twitter、Facebookなど）には使用しないこと。</t>
@@ -913,6 +933,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>./scheme</t>
   </si>
   <si>
@@ -922,16 +946,16 @@
     <t>Patient.telecom.value</t>
   </si>
   <si>
-    <t>The actual contact point details</t>
-  </si>
-  <si>
-    <t>The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
+    <t>実際の連絡先の詳細 / The actual contact point details</t>
+  </si>
+  <si>
+    <t>指定されたコミュニケーションシステムに意味がある形式での実際の連絡先の詳細（電話番号または電子メールアドレス）を提供してください。 / The actual contact point details, in a form that is meaningful to the designated communication system (i.e. phone number or email address).</t>
   </si>
   <si>
     <t>連絡先の番号やメールアドレス</t>
   </si>
   <si>
-    <t>Need to support legacy numbers that are not in a tightly controlled format.</t>
+    <t>厳密に管理された形式でないレガシー番号をサポートする必要がある。 / Need to support legacy numbers that are not in a tightly controlled format.</t>
   </si>
   <si>
     <t>ContactPoint.value</t>
@@ -949,7 +973,7 @@
     <t>home | work | temp | old | mobile - 連絡先の用途等 【詳細参照】</t>
   </si>
   <si>
-    <t>Identifies the purpose for the contact point.</t>
+    <t>接点の目的を特定する。 / Identifies the purpose for the contact point.</t>
   </si>
   <si>
     <t>患者の連絡先の種別をValueSet(ContactPointUse)より選択する。   一時的なものまたは古いものであると明示しない限り、連絡先が最新とみなされる。  
@@ -960,7 +984,7 @@
 　- mobile : モバイル機器</t>
   </si>
   <si>
-    <t>Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
+    <t>人がこの連絡先をどのように使用するかを追跡し、ユーザーが目的に適したものを選択できるようにする必要がある。 / Need to track the way a person uses this contact, so a user can choose which is appropriate for their purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/contact-point-use|4.3.0</t>
@@ -982,10 +1006,10 @@
 </t>
   </si>
   <si>
-    <t>Specify preferred order of use (1 = highest)</t>
-  </si>
-  <si>
-    <t>Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
+    <t>使用の優先順位を指定してください（1が最も優先度が高い） / Specify preferred order of use (1 = highest)</t>
+  </si>
+  <si>
+    <t>一連のコンタクトを使う上で好ましい順序を指定します。ランク値が低いContactPointsの方が、ランク値が高いものよりも優先されます。 / Specifies a preferred order in which to use a set of contacts. ContactPoints with lower rank values are more preferred than those with higher rank values.</t>
   </si>
   <si>
     <t>連絡先の使用順序（1 = 最高）</t>
@@ -997,10 +1021,10 @@
     <t>Patient.telecom.period</t>
   </si>
   <si>
-    <t>Time period when the contact point was/is in use</t>
-  </si>
-  <si>
-    <t>Time period when the contact point was/is in use.</t>
+    <t>コンタクトポイントが使用されている時間帯 / Time period when the contact point was/is in use</t>
+  </si>
+  <si>
+    <t>接点が使用されていた/現在使用中である時間期間 / Time period when the contact point was/is in use.</t>
   </si>
   <si>
     <t>連絡先が使用されていた/されている期間</t>
@@ -1015,7 +1039,7 @@
     <t>Patient.gender</t>
   </si>
   <si>
-    <t>male | female | other | unknown</t>
+    <t>男性|女性|その他|わからない / male | female | other | unknown</t>
   </si>
   <si>
     <t>管理上の性別-患者が管理および記録管理の目的で持つと見なされる性別。</t>
@@ -1028,10 +1052,10 @@
 　unknown 不明</t>
   </si>
   <si>
-    <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
-  </si>
-  <si>
-    <t>The gender of a person used for administrative purposes.</t>
+    <t>（少なくとも）名前と生年月日と組み合わせて、個人の識別に必要です。 / Needed for identification of the individual, in combination with (at least) name and birth date.</t>
+  </si>
+  <si>
+    <t>管理目的で使用される人の性別。 / The gender of a person used for administrative purposes.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.3.0</t>
@@ -1061,7 +1085,7 @@
 例：1945-08-23</t>
   </si>
   <si>
-    <t>Age of the individual drives many clinical processes.</t>
+    <t>個人の年齢は、多くの臨床プロセスを推進します。 / Age of the individual drives many clinical processes.</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/birthTime</t>
@@ -1095,7 +1119,7 @@
 　- deceasedDateTime : 患者の死亡日時</t>
   </si>
   <si>
-    <t>The fact that a patient is deceased influences the clinical process. Also, in human communication and relation management it is necessary to know whether the person is alive.</t>
+    <t>患者が亡くなったという事実は、臨床プロセスに影響を与えます。また、人間のコミュニケーションと関係管理において、その人が生きているかどうかを知る必要があります。 / The fact that a patient is deceased influences the clinical process. Also, in human communication and relation management it is necessary to know whether the person is alive.</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/deceasedInd, player[classCode=PSN|ANM and determinerCode=INSTANCE]/deceasedTime</t>
@@ -1125,7 +1149,7 @@
 ※診療文書構造化記述規約等では、streetAddressLine (FHIRではlineに対応) に指定するとなっていた。</t>
   </si>
   <si>
-    <t>May need to keep track of patient addresses for contacting, billing or reporting requirements and also to help with identification.</t>
+    <t>連絡、請求、報告の要件のために患者の住所を追跡し、識別を支援する必要がある場合があります。 / May need to keep track of patient addresses for contacting, billing or reporting requirements and also to help with identification.</t>
   </si>
   <si>
     <t>addr</t>
@@ -1161,13 +1185,13 @@
 　- billing : 請求書、インボイス、領収書などの送付用</t>
   </si>
   <si>
-    <t>Allows an appropriate address to be chosen from a list of many.</t>
+    <t>多くのリストから適切なアドレスを選択できるようにします。 / Allows an appropriate address to be chosen from a list of many.</t>
   </si>
   <si>
     <t>home</t>
   </si>
   <si>
-    <t>The use of an address (home / work / etc.).</t>
+    <t>住所の用途（自宅 / 勤務先など）。 / The use of an address (home / work / etc.).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/address-use|4.3.0</t>
@@ -1197,7 +1221,7 @@
     <t>both</t>
   </si>
   <si>
-    <t>The type of an address (physical / postal).</t>
+    <t>住所の種類（物理的 / 郵便）。 / The type of an address (physical / postal).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/address-type|4.3.0</t>
@@ -1226,7 +1250,7 @@
 例：東京都文京区本郷7-3-1</t>
   </si>
   <si>
-    <t>A renderable, unencoded form.</t>
+    <t>レンダリング可能で、不コード化されていないフォーム。 / A renderable, unencoded form.</t>
   </si>
   <si>
     <t>137 Nowhere Street, Erewhon 9132</t>
@@ -1308,7 +1332,7 @@
     <t>地区名 【詳細参照】</t>
   </si>
   <si>
-    <t>The name of the administrative area (county).</t>
+    <t>管理エリア（郡）の名前。 / The name of the administrative area (county).</t>
   </si>
   <si>
     <t>【JP Core仕様】日本の住所では使用しない。</t>
@@ -1361,7 +1385,7 @@
     <t>郵便番号 【詳細参照】</t>
   </si>
   <si>
-    <t>A postal code designating a region defined by the postal service.</t>
+    <t>郵便サービスによって定義された地域を指定する郵便番号。 / A postal code designating a region defined by the postal service.</t>
   </si>
   <si>
     <t>郵便番号。日本の郵便番号の場合には3桁数字とハイフン1文字と4桁数字からなる半角８文字、または最初の3桁だけの3文字のいずれかとする。 例：113-8655</t>
@@ -1409,7 +1433,7 @@
     <t>住所が使用されていた/されている期間。 期間は時間の範囲を指定する。使用状況はその期間全体に適用されるか、範囲から1つの値が適用される。  期間は、時間間隔（経過時間の測定値）には使用されない。</t>
   </si>
   <si>
-    <t>Allows addresses to be placed in historical context.</t>
+    <t>アドレスを履歴上の文脈に配置できるようにします。 / Allows addresses to be placed in historical context.</t>
   </si>
   <si>
     <t>&lt;valuePeriod xmlns="http://hl7.org/fhir"&gt;
@@ -1447,10 +1471,10 @@
 　UNK : 不明</t>
   </si>
   <si>
-    <t>Most, if not all systems capture it.</t>
-  </si>
-  <si>
-    <t>The domestic partnership status of a person.</t>
+    <t>ほとんどの場合、すべてではないにしても、それをキャプチャします。 / Most, if not all systems capture it.</t>
+  </si>
+  <si>
+    <t>人の国内パートナーシップの状況。 / The domestic partnership status of a person.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/marital-status|4.3.0</t>
@@ -1541,8 +1565,8 @@
     <t>患者について連絡できる人を確認する必要がある。</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-pat-1:SHALL at least contain a contact's details or a reference to an organization {name.exists() or telecom.exists() or address.exists() or organization.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+pat-1:少なくとも連絡先の詳細または組織への参照を含めるものとする / SHALL at least contain a contact's details or a reference to an organization {name.exists() or telecom.exists() or address.exists() or organization.exists()}</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/scopedRole[classCode=CON]</t>
@@ -1561,10 +1585,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1593,7 +1618,7 @@
     <t>状況に応じて、アプローチするのに最適な関係者を決定するために使用される。</t>
   </si>
   <si>
-    <t>The nature of the relationship between a patient and a contact person for that patient.</t>
+    <t>その患者の患者と接触者との関係の性質。 / The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.3.0</t>
@@ -1612,7 +1637,7 @@
 </t>
   </si>
   <si>
-    <t>A name associated with the contact person</t>
+    <t>連絡先に関連付けられた名前 / A name associated with the contact person</t>
   </si>
   <si>
     <t>連絡先に登録された名前。</t>
@@ -1627,7 +1652,7 @@
     <t>Patient.contact.telecom</t>
   </si>
   <si>
-    <t>A contact detail for the person</t>
+    <t>人の連絡先の詳細 / A contact detail for the person</t>
   </si>
   <si>
     <t>連絡先に登録された連絡方法（電話番号やメールアドレスなど）。</t>
@@ -1645,7 +1670,7 @@
     <t>Patient.contact.address</t>
   </si>
   <si>
-    <t>Address for the contact person</t>
+    <t>連絡先の住所 / Address for the contact person</t>
   </si>
   <si>
     <t>連絡先の住所。</t>
@@ -1672,7 +1697,7 @@
     <t>Patient.contact.organization</t>
   </si>
   <si>
-    <t>Organization that is associated with the contact</t>
+    <t>連絡先に関連する組織 / Organization that is associated with the contact</t>
   </si>
   <si>
     <t>連絡先が主として活動する、または勤務している組織。</t>
@@ -1681,7 +1706,7 @@
     <t>連絡先に関連する組織</t>
   </si>
   <si>
-    <t>For guardians or business related contacts, the organization is relevant.</t>
+    <t>保護者またはビジネス関連の連絡先については、組織が関連しています。 / For guardians or business related contacts, the organization is relevant.</t>
   </si>
   <si>
     <t xml:space="preserve">pat-1
@@ -1697,7 +1722,7 @@
     <t>Patient.contact.period</t>
   </si>
   <si>
-    <t>The period during which this contact person or organization is valid to be contacted relating to this patient</t>
+    <t>この患者に関連するこの連絡先または組織が連絡するのが有効な期間 / The period during which this contact person or organization is valid to be contacted relating to this patient</t>
   </si>
   <si>
     <t>この患者に関連して、この連絡担当者または組織に連絡することが有効な期間。</t>
@@ -1721,7 +1746,7 @@
     <t>患者が現地の言語を話さない場合、通訳が必要になる場合があるため、話せる言語と習熟度は、患者と関心のある他の人の両方にとって注意すべき重要な事項である。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1773,7 +1798,7 @@
     <t>Patient.communication.preferred</t>
   </si>
   <si>
-    <t>Language preference indicator</t>
+    <t>言語選好インジケーター / Language preference indicator</t>
   </si>
   <si>
     <t>患者がこの言語を優先するかどうかを示す（他の言語よりも特定レベルまで習得している）。</t>
@@ -1840,7 +1865,7 @@
     <t>Patient.link</t>
   </si>
   <si>
-    <t>Link to another patient resource that concerns the same actual person</t>
+    <t>同じ実際の人に関係する別の患者リソースへのリンク / Link to another patient resource that concerns the same actual person</t>
   </si>
   <si>
     <t>事実上の同一患者をリンクする別のPatientリソース。</t>
@@ -1873,7 +1898,7 @@
 </t>
   </si>
   <si>
-    <t>The other patient or related person resource that the link refers to</t>
+    <t>リンクが指す他の患者または関連者のリソース / The other patient or related person resource that the link refers to</t>
   </si>
   <si>
     <t>リンクが参照する他の患者リソース。</t>
@@ -1901,7 +1926,7 @@
 　- seealso : このリンクを含む患者リソースは使用中で有効であるが、同じ人物に関するデータが含まれていることがわかっている別の患者リソースを指す</t>
   </si>
   <si>
-    <t>The type of link between this patient resource and another patient resource.</t>
+    <t>この患者リソースと別の患者リソースとの間のリンクのタイプ。 / The type of link between this patient resource and another patient resource.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/link-type|4.3.0</t>
@@ -2238,7 +2263,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="69.35546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="90.19140625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="48.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -5230,10 +5255,10 @@
         <v>93</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>183</v>
+        <v>273</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5316,10 +5341,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5345,13 +5370,13 @@
         <v>137</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>168</v>
+        <v>277</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5413,7 +5438,7 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>143</v>
+        <v>278</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>185</v>
@@ -5433,10 +5458,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5462,13 +5487,13 @@
         <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5498,7 +5523,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5516,7 +5541,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5525,13 +5550,13 @@
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
@@ -5540,7 +5565,7 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5548,10 +5573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5577,16 +5602,16 @@
         <v>220</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5635,7 +5660,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5647,10 +5672,10 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
@@ -5659,7 +5684,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5667,10 +5692,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5696,16 +5721,16 @@
         <v>111</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5734,7 +5759,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5752,7 +5777,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5764,10 +5789,10 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>82</v>
@@ -5776,7 +5801,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5784,10 +5809,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5810,16 +5835,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5869,7 +5894,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5881,7 +5906,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>185</v>
@@ -5901,10 +5926,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5930,13 +5955,13 @@
         <v>229</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5986,7 +6011,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5998,10 +6023,10 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
@@ -6018,10 +6043,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6047,16 +6072,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6084,10 +6109,10 @@
         <v>196</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6105,7 +6130,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6120,16 +6145,16 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6137,10 +6162,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6163,19 +6188,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6224,7 +6249,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6239,27 +6264,27 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6282,19 +6307,19 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6343,7 +6368,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6358,7 +6383,7 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>185</v>
@@ -6367,7 +6392,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6375,10 +6400,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6401,19 +6426,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6462,7 +6487,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6477,16 +6502,16 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6494,10 +6519,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6609,10 +6634,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6726,10 +6751,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6755,16 +6780,16 @@
         <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6777,7 +6802,7 @@
         <v>82</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>82</v>
@@ -6792,10 +6817,10 @@
         <v>196</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6813,7 +6838,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6828,7 +6853,7 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
@@ -6837,7 +6862,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6845,10 +6870,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6874,13 +6899,13 @@
         <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6894,7 +6919,7 @@
         <v>82</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>82</v>
@@ -6909,10 +6934,10 @@
         <v>196</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6930,7 +6955,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6945,7 +6970,7 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
@@ -6954,7 +6979,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6962,10 +6987,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6991,16 +7016,16 @@
         <v>220</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7013,7 +7038,7 @@
         <v>82</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>82</v>
@@ -7049,7 +7074,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7064,7 +7089,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -7073,7 +7098,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7081,10 +7106,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7110,13 +7135,13 @@
         <v>220</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7130,7 +7155,7 @@
         <v>82</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>82</v>
@@ -7166,7 +7191,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7181,7 +7206,7 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
@@ -7190,7 +7215,7 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7198,14 +7223,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7227,13 +7252,13 @@
         <v>220</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7247,7 +7272,7 @@
         <v>82</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>82</v>
@@ -7283,7 +7308,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7298,7 +7323,7 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
@@ -7307,7 +7332,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7315,14 +7340,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7344,13 +7369,13 @@
         <v>220</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7364,7 +7389,7 @@
         <v>82</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>82</v>
@@ -7400,7 +7425,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7415,7 +7440,7 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
@@ -7424,7 +7449,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7432,14 +7457,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7461,13 +7486,13 @@
         <v>220</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7517,7 +7542,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7532,7 +7557,7 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
@@ -7541,7 +7566,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7549,14 +7574,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7578,13 +7603,13 @@
         <v>220</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7598,7 +7623,7 @@
         <v>82</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>82</v>
@@ -7634,7 +7659,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7649,7 +7674,7 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
@@ -7658,7 +7683,7 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7666,10 +7691,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7695,13 +7720,13 @@
         <v>220</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7751,7 +7776,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7766,7 +7791,7 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
@@ -7775,7 +7800,7 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7783,10 +7808,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7812,16 +7837,16 @@
         <v>229</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7834,7 +7859,7 @@
         <v>82</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>82</v>
@@ -7870,7 +7895,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7885,7 +7910,7 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
@@ -7894,7 +7919,7 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7902,10 +7927,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7931,16 +7956,16 @@
         <v>201</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7968,10 +7993,10 @@
         <v>206</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7989,7 +8014,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8004,16 +8029,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8021,10 +8046,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8047,19 +8072,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8108,7 +8133,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8123,7 +8148,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>185</v>
@@ -8132,7 +8157,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8140,10 +8165,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8166,19 +8191,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8227,7 +8252,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8242,7 +8267,7 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>185</v>
@@ -8251,7 +8276,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8259,10 +8284,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8285,19 +8310,19 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8346,7 +8371,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8358,10 +8383,10 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>185</v>
@@ -8378,10 +8403,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8493,10 +8518,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8610,14 +8635,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8639,10 +8664,10 @@
         <v>137</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>168</v>
@@ -8697,7 +8722,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8729,10 +8754,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8758,16 +8783,16 @@
         <v>201</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8795,10 +8820,10 @@
         <v>206</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8816,7 +8841,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8831,7 +8856,7 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>185</v>
@@ -8840,7 +8865,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8848,10 +8873,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8874,17 +8899,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8933,7 +8958,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8957,7 +8982,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8965,10 +8990,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8994,16 +9019,16 @@
         <v>263</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9052,7 +9077,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9076,7 +9101,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9084,10 +9109,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9110,17 +9135,17 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9169,7 +9194,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9184,7 +9209,7 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>185</v>
@@ -9193,7 +9218,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9201,10 +9226,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9230,14 +9255,14 @@
         <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9265,10 +9290,10 @@
         <v>196</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9286,7 +9311,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9301,7 +9326,7 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>185</v>
@@ -9310,7 +9335,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9318,10 +9343,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9347,16 +9372,16 @@
         <v>237</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9405,7 +9430,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9414,13 +9439,13 @@
         <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>185</v>
@@ -9429,7 +9454,7 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9437,10 +9462,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9466,10 +9491,10 @@
         <v>229</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9520,7 +9545,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9535,7 +9560,7 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>185</v>
@@ -9552,10 +9577,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9578,19 +9603,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9639,7 +9664,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9651,13 +9676,13 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
@@ -9671,10 +9696,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9786,10 +9811,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9903,14 +9928,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9932,10 +9957,10 @@
         <v>137</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>168</v>
@@ -9990,7 +10015,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10022,10 +10047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10051,16 +10076,16 @@
         <v>201</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10109,7 +10134,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>91</v>
@@ -10124,16 +10149,16 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10141,10 +10166,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10170,16 +10195,16 @@
         <v>245</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10228,7 +10253,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10243,16 +10268,16 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10260,14 +10285,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10286,16 +10311,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10345,7 +10370,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10360,7 +10385,7 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>185</v>
@@ -10369,7 +10394,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10377,10 +10402,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10406,16 +10431,16 @@
         <v>237</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10464,7 +10489,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10479,10 +10504,10 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>82</v>
@@ -10496,10 +10521,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10522,19 +10547,19 @@
         <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10583,7 +10608,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10595,10 +10620,10 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>185</v>
@@ -10615,10 +10640,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10730,10 +10755,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10847,14 +10872,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10876,10 +10901,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>168</v>
@@ -10934,7 +10959,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10966,10 +10991,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10992,16 +11017,16 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11051,7 +11076,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>91</v>
@@ -11075,7 +11100,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11083,10 +11108,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11112,13 +11137,13 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11147,10 +11172,10 @@
         <v>196</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11168,7 +11193,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>91</v>
@@ -11183,7 +11208,7 @@
         <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>185</v>
